--- a/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11014</v>
+        <v>923</v>
       </c>
       <c r="C2" t="n">
-        <v>113.5463917525773</v>
+        <v>10.14285714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>490.9980062039152</v>
+        <v>33.00052909628754</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3259</v>
+        <v>246</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>923</v>
+        <v>26509.89622641509</v>
       </c>
       <c r="C2" t="n">
-        <v>10.14285714285714</v>
+        <v>276.1447523584906</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>33.00052909628754</v>
+        <v>1330.158127025462</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>246</v>
+        <v>8152</v>
       </c>
       <c r="H2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26509.89622641509</v>
+        <v>22999.89523809524</v>
       </c>
       <c r="C2" t="n">
-        <v>276.1447523584906</v>
+        <v>242.1041604010025</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1330.158127025462</v>
+        <v>1536.46403768565</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8152</v>
+        <v>14525</v>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I2" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
